--- a/assets/Nomina con detalle de alt.xlsx
+++ b/assets/Nomina con detalle de alt.xlsx
@@ -1869,15 +1869,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89C80661-C5D7-49F5-BBA0-CA51D7F75AD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F21923D9-E981-4C1E-9A73-48D2C6715AA7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CAFA27D-17E4-4B6D-BDFB-0B612D323F57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{070DCF47-0512-4FD8-9F01-FE711A8C2FC4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{830F0B89-B932-4B60-B01B-45D08474403C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F840984-2573-42D7-A798-349603BB0E47}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
